--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260806.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260806.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>149,535</t>
+          <t>149,185</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>29.61%</t>
+          <t>29.95%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.19%</t>
+          <t>8.11%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>108,470</t>
+          <t>108,120</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.42%</t>
+          <t>7.40%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>55,275</t>
+          <t>55,075</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.53%</t>
+          <t>5.54%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>131,645</t>
+          <t>131,445</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.36%</t>
+          <t>5.31%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>64,730</t>
+          <t>64,630</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>71,235</t>
+          <t>71,035</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>49,215</t>
+          <t>49,115</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,883</t>
+          <t>19,783</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>83,605</t>
+          <t>83,505</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -924,271 +924,271 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>28,848</t>
+          <t>3,662,888</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>39,320</t>
+          <t>28,748</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>21,180</t>
+          <t>39,220</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>64,548</t>
+          <t>96,050,801</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>12,691</t>
+          <t>21,080</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>8,660</t>
+          <t>64,448</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>23,118</t>
+          <t>8,660</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>79,815,301</t>
+          <t>23,018</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>137,945</t>
+          <t>10,336</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>10,436</t>
+          <t>12,591</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>20,005</t>
+          <t>137,645</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>21,277</t>
+          <t>19,905</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1205,100 +1205,100 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>17,221</t>
+          <t>17,121</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>40,750</t>
+          <t>21,177</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>46,940</t>
+          <t>40,650</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>12,655</t>
+          <t>46,840</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,238,909</t>
+          <t>12,655</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>100,228,500</t>
+          <t>100,119,500</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2,923,980</t>
+          <t>466,194</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
